--- a/testdata/lead/bulk_upload/rahul_contact.xlsx
+++ b/testdata/lead/bulk_upload/rahul_contact.xlsx
@@ -412,57 +412,57 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Sameer Chopra</v>
+        <v>Malti Talwar</v>
       </c>
       <c r="B2" t="str">
-        <v>sameer.chopra323@gmail.com</v>
+        <v>malti.talwar192@gmail.com</v>
       </c>
       <c r="C2">
-        <v>6313324489</v>
+        <v>6313519605</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Aayushman Patel</v>
+        <v>Chaaruchandra Kaniyar</v>
       </c>
       <c r="B3" t="str">
-        <v>aayushman.patel174@gmail.com</v>
+        <v>chaaruchandra.kaniyar457@gmail.com</v>
       </c>
       <c r="C3">
-        <v>6332025397</v>
+        <v>8772789786</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Shwet Achari</v>
+        <v>Abhisyanta Ganaka</v>
       </c>
       <c r="B4" t="str">
-        <v>shwet.achari277@gmail.com</v>
+        <v>abhisyanta.ganaka385@gmail.com</v>
       </c>
       <c r="C4">
-        <v>7051593894</v>
+        <v>9740900636</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Sujata Pothuvaal</v>
+        <v>Akshayakeerti Prajapat</v>
       </c>
       <c r="B5" t="str">
-        <v>sujata.pothuvaal661@gmail.com</v>
+        <v>akshayakeerti.prajapat124@gmail.com</v>
       </c>
       <c r="C5">
-        <v>8869800485</v>
+        <v>9783928277</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Tara Bhat</v>
+        <v>Amrita Suthar</v>
       </c>
       <c r="B6" t="str">
-        <v>tara.bhat698@gmail.com</v>
+        <v>amrita.suthar841@gmail.com</v>
       </c>
       <c r="C6">
-        <v>9823355851</v>
+        <v>9978155987</v>
       </c>
     </row>
   </sheetData>
